--- a/Konekcije.xlsx
+++ b/Konekcije.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleksandra.seva\Desktop\DIAG_XML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleksandra.seva\Desktop\LineFailure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F21B80-7CC4-4EC3-881C-C6054BC644AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568AE350-D4B9-4E8A-A440-741B7DC93C4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="147">
   <si>
     <t>KOZ</t>
   </si>
@@ -163,30 +163,12 @@
     <t>BLK GP</t>
   </si>
   <si>
-    <t>port-1: E1_BG/BLK APP</t>
-  </si>
-  <si>
     <t>port-3: GP zaštitna/BLK APP</t>
   </si>
   <si>
-    <t>port-1: TWR zaštitna_link/BLK GP</t>
-  </si>
-  <si>
-    <t>Port-4 Prespoj BLK APP-Stari MUX APP/BLK APP</t>
-  </si>
-  <si>
-    <t>port-3: MM working/BLK APP</t>
-  </si>
-  <si>
     <t>interfaces/if-1</t>
   </si>
   <si>
-    <t>if-1:BL GP radna/BLK APP</t>
-  </si>
-  <si>
-    <t>if-1 : radna prema BL APP/BLK GP</t>
-  </si>
-  <si>
     <t>PLV</t>
   </si>
   <si>
@@ -442,22 +424,43 @@
     <t>port-4: SJJ4-SJJ1_1/SJJ4 (BTM)</t>
   </si>
   <si>
-    <t>port-2: BTM APP-BTM_1/BTM APP</t>
-  </si>
-  <si>
-    <t>port-1: LL 74 (JPAKL SA-Bukovik)/BTM APP</t>
-  </si>
-  <si>
-    <t>port-1: RR BTM APP-BUK APP/BTM APP</t>
-  </si>
-  <si>
-    <t>RR BTM-BUK APP/BUK APP</t>
-  </si>
-  <si>
     <t>RR UDR-MST_A/UDR</t>
   </si>
   <si>
     <t>RR UDR-MST_B/UDR</t>
+  </si>
+  <si>
+    <t>/BUK (APP)</t>
+  </si>
+  <si>
+    <t>RR BTM-BUK APP/BUK (APP)</t>
+  </si>
+  <si>
+    <t>port-1: LL 74 (JPAKL SA-Bukovik)/BTM (APP)</t>
+  </si>
+  <si>
+    <t>port-1: RR BTM APP-BUK APP/BTM (APP)</t>
+  </si>
+  <si>
+    <t>port-1: E1_BG/BLK (APP)</t>
+  </si>
+  <si>
+    <t>Port-4 Prespoj BLK APP-Stari MUX APP/BLK (APP)</t>
+  </si>
+  <si>
+    <t>port-3: MM working/BLK (APP)</t>
+  </si>
+  <si>
+    <t>if-1:BL GP radna/BLK (APP)</t>
+  </si>
+  <si>
+    <t>port-1: TWR zaštitna_link/BLK (GP)</t>
+  </si>
+  <si>
+    <t>if-1 : radna prema BL APP/BLK (GP)</t>
+  </si>
+  <si>
+    <t>port-2: BTM APP-BTM_1/BTM (APP)</t>
   </si>
 </sst>
 </file>
@@ -1531,6 +1534,96 @@
     <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1540,6 +1633,15 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1549,15 +1651,6 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1574,24 +1667,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1602,78 +1677,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2810,7 +2813,7 @@
   <cols>
     <col min="1" max="1" width="8.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.875" style="1" customWidth="1"/>
@@ -2826,30 +2829,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="132" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="135" t="s">
-        <v>127</v>
-      </c>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="111" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="112"/>
-      <c r="P1" s="113"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="98"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2862,7 +2865,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -2919,11 +2922,11 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="111" t="s">
+      <c r="N3" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="112"/>
-      <c r="P3" s="113"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="98"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" s="18" t="s">
@@ -2987,11 +2990,11 @@
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="123" t="s">
+      <c r="N5" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="124"/>
-      <c r="P5" s="125"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="101"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
       <c r="A6" s="30" t="s">
@@ -3091,11 +3094,11 @@
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="138" t="s">
+      <c r="N8" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="O8" s="139"/>
-      <c r="P8" s="140"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="116"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1">
       <c r="A9" s="44"/>
@@ -3165,11 +3168,11 @@
       <c r="K11" s="46"/>
       <c r="L11" s="46"/>
       <c r="M11" s="47"/>
-      <c r="N11" s="102" t="s">
+      <c r="N11" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="O11" s="103"/>
-      <c r="P11" s="104"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="122"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1">
       <c r="A12" s="29"/>
@@ -3215,11 +3218,11 @@
       <c r="K13" s="46"/>
       <c r="L13" s="46"/>
       <c r="M13" s="47"/>
-      <c r="N13" s="111" t="s">
+      <c r="N13" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="112"/>
-      <c r="P13" s="113"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="98"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="29"/>
@@ -3265,11 +3268,11 @@
       <c r="K15" s="46"/>
       <c r="L15" s="46"/>
       <c r="M15" s="47"/>
-      <c r="N15" s="111" t="s">
+      <c r="N15" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O15" s="112"/>
-      <c r="P15" s="113"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="98"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
       <c r="A16" s="29"/>
@@ -3327,11 +3330,11 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="123" t="s">
+      <c r="N17" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="124"/>
-      <c r="P17" s="125"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="101"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="29"/>
@@ -3377,11 +3380,11 @@
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="102" t="s">
+      <c r="N19" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="O19" s="103"/>
-      <c r="P19" s="104"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="122"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1">
       <c r="A20" s="29"/>
@@ -3450,16 +3453,16 @@
       <c r="P22" s="29"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A23" s="138" t="s">
+      <c r="A23" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141" t="s">
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="142"/>
-      <c r="F23" s="143"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
       <c r="G23" s="28"/>
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
@@ -3479,7 +3482,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="23"/>
@@ -3503,10 +3506,10 @@
         <v>11</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>3</v>
@@ -3533,7 +3536,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
@@ -3557,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="25"/>
@@ -3578,16 +3581,16 @@
         <v>18</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>18</v>
@@ -3640,18 +3643,18 @@
       <c r="P30" s="29"/>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1">
-      <c r="A31" s="126" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="127"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="123" t="s">
+      <c r="A31" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="124"/>
-      <c r="F31" s="124"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="125"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="101"/>
       <c r="I31" s="51"/>
       <c r="J31" s="53"/>
       <c r="K31" s="53"/>
@@ -3669,10 +3672,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -3682,11 +3685,11 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="J32" s="100"/>
-      <c r="K32" s="101"/>
+      <c r="I32" s="132" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" s="133"/>
+      <c r="K32" s="134"/>
       <c r="L32" s="28"/>
       <c r="M32" s="29"/>
       <c r="N32" s="29"/>
@@ -3701,7 +3704,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
@@ -3712,16 +3715,16 @@
         <v>11</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L33" s="28"/>
       <c r="M33" s="29"/>
@@ -3737,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E34" s="31" t="s">
         <v>3</v>
@@ -3750,11 +3753,11 @@
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="105" t="s">
-        <v>65</v>
-      </c>
-      <c r="J34" s="106"/>
-      <c r="K34" s="107"/>
+      <c r="I34" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="136"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="28"/>
       <c r="M34" s="29"/>
       <c r="N34" s="29"/>
@@ -3774,16 +3777,16 @@
         <v>11</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L35" s="28"/>
       <c r="M35" s="29"/>
@@ -3864,16 +3867,16 @@
       <c r="P39" s="29"/>
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A40" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="100"/>
-      <c r="C40" s="101"/>
-      <c r="D40" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="E40" s="100"/>
-      <c r="F40" s="101"/>
+      <c r="A40" s="132" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="133"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="133"/>
+      <c r="F40" s="134"/>
       <c r="G40" s="28"/>
       <c r="H40" s="29"/>
       <c r="I40" s="29"/>
@@ -3893,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="23"/>
@@ -3917,10 +3920,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -3947,7 +3950,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="14"/>
@@ -3971,7 +3974,7 @@
         <v>31</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="25"/>
@@ -3989,22 +3992,22 @@
     </row>
     <row r="45" spans="1:16" ht="15.95" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E45" s="31" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G45" s="28"/>
       <c r="H45" s="29"/>
@@ -4019,13 +4022,13 @@
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B46" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="69" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="70"/>
@@ -4132,25 +4135,25 @@
       <c r="P51" s="29"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1">
-      <c r="A52" s="102" t="s">
+      <c r="A52" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="103"/>
-      <c r="C52" s="104"/>
-      <c r="D52" s="108" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="109"/>
-      <c r="G52" s="109"/>
-      <c r="H52" s="110"/>
-      <c r="I52" s="111" t="s">
+      <c r="B52" s="121"/>
+      <c r="C52" s="122"/>
+      <c r="D52" s="138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
+      <c r="H52" s="140"/>
+      <c r="I52" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="J52" s="112"/>
-      <c r="K52" s="112"/>
-      <c r="L52" s="112"/>
-      <c r="M52" s="113"/>
+      <c r="J52" s="97"/>
+      <c r="K52" s="97"/>
+      <c r="L52" s="97"/>
+      <c r="M52" s="98"/>
       <c r="N52" s="51"/>
       <c r="O52" s="53"/>
       <c r="P52" s="53"/>
@@ -4169,11 +4172,11 @@
       <c r="K53" s="79"/>
       <c r="L53" s="79"/>
       <c r="M53" s="80"/>
-      <c r="N53" s="114" t="s">
-        <v>76</v>
-      </c>
-      <c r="O53" s="115"/>
-      <c r="P53" s="116"/>
+      <c r="N53" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="O53" s="130"/>
+      <c r="P53" s="131"/>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
@@ -4183,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -4205,10 +4208,10 @@
         <v>11</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="O54" s="11" t="s">
         <v>10</v>
@@ -4230,10 +4233,10 @@
         <v>7</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>10</v>
@@ -4255,10 +4258,10 @@
         <v>11</v>
       </c>
       <c r="C56" s="81" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>11</v>
@@ -4277,13 +4280,13 @@
         <v>28</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="N56" s="96" t="s">
-        <v>83</v>
-      </c>
-      <c r="O56" s="97"/>
-      <c r="P56" s="98"/>
+        <v>76</v>
+      </c>
+      <c r="N56" s="126" t="s">
+        <v>77</v>
+      </c>
+      <c r="O56" s="127"/>
+      <c r="P56" s="128"/>
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1">
       <c r="A57" s="18" t="s">
@@ -4293,10 +4296,10 @@
         <v>10</v>
       </c>
       <c r="C57" s="81" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>10</v>
@@ -4315,10 +4318,10 @@
         <v>31</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O57" s="11" t="s">
         <v>10</v>
@@ -4335,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="C58" s="81" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>3</v>
@@ -4365,10 +4368,10 @@
         <v>7</v>
       </c>
       <c r="C59" s="81" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>7</v>
@@ -4395,10 +4398,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="43" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>11</v>
@@ -4430,10 +4433,10 @@
         <v>10</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>11</v>
@@ -4461,11 +4464,11 @@
       <c r="K62" s="46"/>
       <c r="L62" s="88"/>
       <c r="M62" s="26"/>
-      <c r="N62" s="114" t="s">
-        <v>76</v>
-      </c>
-      <c r="O62" s="115"/>
-      <c r="P62" s="116"/>
+      <c r="N62" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="O62" s="130"/>
+      <c r="P62" s="131"/>
     </row>
     <row r="63" spans="1:16" ht="15" customHeight="1">
       <c r="A63" s="29"/>
@@ -4485,10 +4488,10 @@
         <v>10</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O63" s="11" t="s">
         <v>10</v>
@@ -4511,11 +4514,11 @@
       <c r="K64" s="23"/>
       <c r="L64" s="23"/>
       <c r="M64" s="6"/>
-      <c r="N64" s="96" t="s">
-        <v>83</v>
-      </c>
-      <c r="O64" s="97"/>
-      <c r="P64" s="98"/>
+      <c r="N64" s="126" t="s">
+        <v>77</v>
+      </c>
+      <c r="O64" s="127"/>
+      <c r="P64" s="128"/>
     </row>
     <row r="65" spans="1:16" ht="15" customHeight="1">
       <c r="A65" s="29"/>
@@ -4535,10 +4538,10 @@
         <v>31</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O65" s="11" t="s">
         <v>10</v>
@@ -4565,7 +4568,7 @@
         <v>34</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="N66" s="82"/>
       <c r="O66" s="44"/>
@@ -4662,18 +4665,18 @@
       <c r="P71" s="29"/>
     </row>
     <row r="72" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A72" s="117" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" s="118"/>
-      <c r="C72" s="119"/>
-      <c r="D72" s="114" t="s">
-        <v>76</v>
-      </c>
-      <c r="E72" s="115"/>
-      <c r="F72" s="115"/>
-      <c r="G72" s="115"/>
-      <c r="H72" s="116"/>
+      <c r="A72" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="B72" s="142"/>
+      <c r="C72" s="143"/>
+      <c r="D72" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="E72" s="130"/>
+      <c r="F72" s="130"/>
+      <c r="G72" s="130"/>
+      <c r="H72" s="131"/>
       <c r="I72" s="28"/>
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
@@ -4691,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>3</v>
@@ -4721,10 +4724,10 @@
         <v>11</v>
       </c>
       <c r="C74" s="56" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E74" s="36" t="s">
         <v>11</v>
@@ -4748,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C75" s="38"/>
       <c r="D75" s="28"/>
@@ -4760,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I75" s="28"/>
       <c r="J75" s="29"/>
@@ -4779,10 +4782,10 @@
         <v>3</v>
       </c>
       <c r="C76" s="81" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>3</v>
@@ -4809,10 +4812,10 @@
         <v>7</v>
       </c>
       <c r="C77" s="81" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>7</v>
@@ -4839,10 +4842,10 @@
         <v>11</v>
       </c>
       <c r="C78" s="43" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D78" s="41" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E78" s="42" t="s">
         <v>11</v>
@@ -4901,30 +4904,30 @@
       <c r="A81" s="53"/>
       <c r="B81" s="53"/>
       <c r="C81" s="89"/>
-      <c r="D81" s="111" t="s">
-        <v>106</v>
-      </c>
-      <c r="E81" s="112"/>
-      <c r="F81" s="112"/>
-      <c r="G81" s="112"/>
-      <c r="H81" s="113"/>
-      <c r="I81" s="96" t="s">
-        <v>83</v>
-      </c>
-      <c r="J81" s="97"/>
-      <c r="K81" s="97"/>
-      <c r="L81" s="97"/>
-      <c r="M81" s="98"/>
+      <c r="D81" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="E81" s="97"/>
+      <c r="F81" s="97"/>
+      <c r="G81" s="97"/>
+      <c r="H81" s="98"/>
+      <c r="I81" s="126" t="s">
+        <v>77</v>
+      </c>
+      <c r="J81" s="127"/>
+      <c r="K81" s="127"/>
+      <c r="L81" s="127"/>
+      <c r="M81" s="128"/>
       <c r="N81" s="28"/>
       <c r="O81" s="29"/>
       <c r="P81" s="29"/>
     </row>
     <row r="82" spans="1:16" ht="15" customHeight="1">
-      <c r="A82" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="B82" s="100"/>
-      <c r="C82" s="101"/>
+      <c r="A82" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="B82" s="133"/>
+      <c r="C82" s="134"/>
       <c r="D82" s="13"/>
       <c r="E82" s="16"/>
       <c r="F82" s="3" t="s">
@@ -4934,10 +4937,10 @@
         <v>3</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>3</v>
@@ -4964,10 +4967,10 @@
         <v>11</v>
       </c>
       <c r="H83" s="56" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J83" s="36" t="s">
         <v>11</v>
@@ -4977,11 +4980,11 @@
       </c>
       <c r="L83" s="25"/>
       <c r="M83" s="26"/>
-      <c r="N83" s="105" t="s">
-        <v>65</v>
-      </c>
-      <c r="O83" s="106"/>
-      <c r="P83" s="107"/>
+      <c r="N83" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="O83" s="136"/>
+      <c r="P83" s="137"/>
     </row>
     <row r="84" spans="1:16" ht="15" customHeight="1">
       <c r="A84" s="10" t="s">
@@ -4991,10 +4994,10 @@
         <v>7</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>10</v>
@@ -5013,10 +5016,10 @@
         <v>28</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N84" s="90" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="O84" s="90" t="s">
         <v>3</v>
@@ -5039,11 +5042,11 @@
       <c r="K85" s="23"/>
       <c r="L85" s="23"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="114" t="s">
-        <v>76</v>
-      </c>
-      <c r="O85" s="115"/>
-      <c r="P85" s="116"/>
+      <c r="N85" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="O85" s="130"/>
+      <c r="P85" s="131"/>
     </row>
     <row r="86" spans="1:16" ht="15" customHeight="1">
       <c r="A86" s="29"/>
@@ -5063,10 +5066,10 @@
         <v>31</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="O86" s="11" t="s">
         <v>7</v>
@@ -5088,10 +5091,10 @@
         <v>3</v>
       </c>
       <c r="H87" s="81" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J87" s="19" t="s">
         <v>3</v>
@@ -5118,10 +5121,10 @@
         <v>7</v>
       </c>
       <c r="H88" s="81" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J88" s="19" t="s">
         <v>7</v>
@@ -5148,10 +5151,10 @@
         <v>11</v>
       </c>
       <c r="H89" s="43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J89" s="59" t="s">
         <v>11</v>
@@ -5161,11 +5164,11 @@
       </c>
       <c r="L89" s="25"/>
       <c r="M89" s="26"/>
-      <c r="N89" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="O89" s="100"/>
-      <c r="P89" s="101"/>
+      <c r="N89" s="132" t="s">
+        <v>52</v>
+      </c>
+      <c r="O89" s="133"/>
+      <c r="P89" s="134"/>
     </row>
     <row r="90" spans="1:16" ht="15" customHeight="1">
       <c r="A90" s="29"/>
@@ -5185,10 +5188,10 @@
       </c>
       <c r="L90" s="92"/>
       <c r="M90" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="N90" s="48" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O90" s="49" t="s">
         <v>3</v>
@@ -5211,23 +5214,23 @@
       <c r="K91" s="23"/>
       <c r="L91" s="23"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="114" t="s">
-        <v>76</v>
-      </c>
-      <c r="O91" s="115"/>
-      <c r="P91" s="116"/>
+      <c r="N91" s="129" t="s">
+        <v>70</v>
+      </c>
+      <c r="O91" s="130"/>
+      <c r="P91" s="131"/>
     </row>
     <row r="92" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="A92" s="120" t="s">
-        <v>123</v>
-      </c>
-      <c r="B92" s="121"/>
-      <c r="C92" s="122"/>
-      <c r="D92" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="E92" s="100"/>
-      <c r="F92" s="101"/>
+      <c r="A92" s="123" t="s">
+        <v>117</v>
+      </c>
+      <c r="B92" s="124"/>
+      <c r="C92" s="125"/>
+      <c r="D92" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" s="133"/>
+      <c r="F92" s="134"/>
       <c r="G92" s="28"/>
       <c r="H92" s="38"/>
       <c r="I92" s="93"/>
@@ -5239,10 +5242,10 @@
       </c>
       <c r="L92" s="94"/>
       <c r="M92" s="12" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O92" s="11" t="s">
         <v>28</v>
@@ -5259,10 +5262,10 @@
         <v>28</v>
       </c>
       <c r="C93" s="95" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>3</v>
@@ -5283,22 +5286,22 @@
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A94" s="48" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B94" s="49" t="s">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E94" s="49" t="s">
         <v>3</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G94" s="28"/>
       <c r="H94" s="29"/>
@@ -5313,6 +5316,29 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="I52:M52"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="D81:H81"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="I81:M81"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="N85:P85"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="N17:P17"/>
@@ -5328,29 +5354,6 @@
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="I81:M81"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="I52:M52"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="D72:H72"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>

--- a/Konekcije.xlsx
+++ b/Konekcije.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleksandra.seva\Desktop\LineFailure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568AE350-D4B9-4E8A-A440-741B7DC93C4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EDD3B1-527B-4673-A219-42FDAA8C57C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,9 +112,6 @@
     <t>BLK1-BLK4/BLK1 (SJJ)</t>
   </si>
   <si>
-    <t>port-2: E1 - BL(sa)/BLK APP</t>
-  </si>
-  <si>
     <t>port-6</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>BLK GP</t>
   </si>
   <si>
-    <t>port-3: GP zaštitna/BLK APP</t>
-  </si>
-  <si>
     <t>interfaces/if-1</t>
   </si>
   <si>
@@ -343,9 +337,6 @@
     <t>port-5: LL 15 (SJJ-TZL)/SJJ4 (BTM)</t>
   </si>
   <si>
-    <t>LL 15 (Tuzla - Sarajevo/Nedzarici)/TZL</t>
-  </si>
-  <si>
     <t>port-6: SJJ4-SJJ3_1/SJJ4 (BTM)</t>
   </si>
   <si>
@@ -461,6 +452,15 @@
   </si>
   <si>
     <t>port-2: BTM APP-BTM_1/BTM (APP)</t>
+  </si>
+  <si>
+    <t>port-2: E1 - BL(sa)/BLK (APP)</t>
+  </si>
+  <si>
+    <t>port-3: GP zaštitna/BLK (APP)</t>
+  </si>
+  <si>
+    <t>LL 15 (Tuzla - Nedzarici)/TZL</t>
   </si>
 </sst>
 </file>
@@ -2835,14 +2835,14 @@
       <c r="B1" s="106"/>
       <c r="C1" s="107"/>
       <c r="D1" s="108" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E1" s="109"/>
       <c r="F1" s="109"/>
       <c r="G1" s="109"/>
       <c r="H1" s="110"/>
       <c r="I1" s="111" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J1" s="112"/>
       <c r="K1" s="112"/>
@@ -2865,7 +2865,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -3121,7 +3121,7 @@
         <v>29</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>7</v>
@@ -3145,10 +3145,10 @@
         <v>2</v>
       </c>
       <c r="L10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="N10" s="39"/>
       <c r="O10" s="40"/>
@@ -3169,7 +3169,7 @@
       <c r="L11" s="46"/>
       <c r="M11" s="47"/>
       <c r="N11" s="120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O11" s="121"/>
       <c r="P11" s="122"/>
@@ -3189,13 +3189,13 @@
         <v>2</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="N12" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="O12" s="11" t="s">
         <v>7</v>
@@ -3242,10 +3242,10 @@
         <v>3</v>
       </c>
       <c r="M14" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" s="48" t="s">
         <v>37</v>
-      </c>
-      <c r="N14" s="48" t="s">
-        <v>38</v>
       </c>
       <c r="O14" s="49" t="s">
         <v>3</v>
@@ -3292,10 +3292,10 @@
         <v>7</v>
       </c>
       <c r="M16" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="N16" s="48" t="s">
         <v>39</v>
-      </c>
-      <c r="N16" s="48" t="s">
-        <v>40</v>
       </c>
       <c r="O16" s="49" t="s">
         <v>7</v>
@@ -3317,10 +3317,10 @@
         <v>10</v>
       </c>
       <c r="H17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>11</v>
@@ -3354,10 +3354,10 @@
         <v>10</v>
       </c>
       <c r="M18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="O18" s="11" t="s">
         <v>7</v>
@@ -3381,7 +3381,7 @@
       <c r="L19" s="23"/>
       <c r="M19" s="6"/>
       <c r="N19" s="120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O19" s="121"/>
       <c r="P19" s="122"/>
@@ -3404,10 +3404,10 @@
         <v>28</v>
       </c>
       <c r="M20" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N20" s="48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O20" s="49" t="s">
         <v>10</v>
@@ -3459,7 +3459,7 @@
       <c r="B23" s="115"/>
       <c r="C23" s="116"/>
       <c r="D23" s="117" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="118"/>
       <c r="F23" s="119"/>
@@ -3482,7 +3482,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="23"/>
@@ -3506,10 +3506,10 @@
         <v>11</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>3</v>
@@ -3536,7 +3536,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
@@ -3560,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="25"/>
@@ -3581,16 +3581,16 @@
         <v>18</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>18</v>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1">
       <c r="A31" s="102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31" s="103"/>
       <c r="C31" s="104"/>
@@ -3672,10 +3672,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -3686,7 +3686,7 @@
       <c r="G32" s="5"/>
       <c r="H32" s="6"/>
       <c r="I32" s="132" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J32" s="133"/>
       <c r="K32" s="134"/>
@@ -3704,7 +3704,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
@@ -3715,16 +3715,16 @@
         <v>11</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L33" s="28"/>
       <c r="M33" s="29"/>
@@ -3740,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E34" s="31" t="s">
         <v>3</v>
@@ -3754,7 +3754,7 @@
       <c r="G34" s="5"/>
       <c r="H34" s="6"/>
       <c r="I34" s="135" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J34" s="136"/>
       <c r="K34" s="137"/>
@@ -3777,16 +3777,16 @@
         <v>11</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L35" s="28"/>
       <c r="M35" s="29"/>
@@ -3868,12 +3868,12 @@
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1">
       <c r="A40" s="132" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B40" s="133"/>
       <c r="C40" s="134"/>
       <c r="D40" s="132" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E40" s="133"/>
       <c r="F40" s="134"/>
@@ -3896,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="23"/>
@@ -3920,10 +3920,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -3950,7 +3950,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="14"/>
@@ -3971,10 +3971,10 @@
         <v>18</v>
       </c>
       <c r="B44" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="25"/>
@@ -3992,22 +3992,22 @@
     </row>
     <row r="45" spans="1:16" ht="15.95" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E45" s="31" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G45" s="28"/>
       <c r="H45" s="29"/>
@@ -4022,13 +4022,13 @@
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="70"/>
@@ -4136,12 +4136,12 @@
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1">
       <c r="A52" s="120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52" s="121"/>
       <c r="C52" s="122"/>
       <c r="D52" s="138" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E52" s="139"/>
       <c r="F52" s="139"/>
@@ -4173,7 +4173,7 @@
       <c r="L53" s="79"/>
       <c r="M53" s="80"/>
       <c r="N53" s="129" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O53" s="130"/>
       <c r="P53" s="131"/>
@@ -4186,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -4208,10 +4208,10 @@
         <v>11</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O54" s="11" t="s">
         <v>10</v>
@@ -4233,10 +4233,10 @@
         <v>7</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>10</v>
@@ -4258,10 +4258,10 @@
         <v>11</v>
       </c>
       <c r="C56" s="81" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>11</v>
@@ -4280,10 +4280,10 @@
         <v>28</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N56" s="126" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O56" s="127"/>
       <c r="P56" s="128"/>
@@ -4296,10 +4296,10 @@
         <v>10</v>
       </c>
       <c r="C57" s="81" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>10</v>
@@ -4315,13 +4315,13 @@
         <v>18</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O57" s="11" t="s">
         <v>10</v>
@@ -4338,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="C58" s="81" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>3</v>
@@ -4368,10 +4368,10 @@
         <v>7</v>
       </c>
       <c r="C59" s="81" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>7</v>
@@ -4398,10 +4398,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>11</v>
@@ -4433,10 +4433,10 @@
         <v>10</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>11</v>
@@ -4465,7 +4465,7 @@
       <c r="L62" s="88"/>
       <c r="M62" s="26"/>
       <c r="N62" s="129" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O62" s="130"/>
       <c r="P62" s="131"/>
@@ -4488,10 +4488,10 @@
         <v>10</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="O63" s="11" t="s">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       <c r="L64" s="23"/>
       <c r="M64" s="6"/>
       <c r="N64" s="126" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O64" s="127"/>
       <c r="P64" s="128"/>
@@ -4535,13 +4535,13 @@
         <v>2</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O65" s="11" t="s">
         <v>10</v>
@@ -4565,10 +4565,10 @@
         <v>2</v>
       </c>
       <c r="L66" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N66" s="82"/>
       <c r="O66" s="44"/>
@@ -4666,12 +4666,12 @@
     </row>
     <row r="72" spans="1:16" ht="16.5" customHeight="1">
       <c r="A72" s="141" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B72" s="142"/>
       <c r="C72" s="143"/>
       <c r="D72" s="129" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E72" s="130"/>
       <c r="F72" s="130"/>
@@ -4694,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>3</v>
@@ -4724,10 +4724,10 @@
         <v>11</v>
       </c>
       <c r="C74" s="56" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E74" s="36" t="s">
         <v>11</v>
@@ -4751,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C75" s="38"/>
       <c r="D75" s="28"/>
@@ -4763,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I75" s="28"/>
       <c r="J75" s="29"/>
@@ -4782,10 +4782,10 @@
         <v>3</v>
       </c>
       <c r="C76" s="81" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>3</v>
@@ -4812,10 +4812,10 @@
         <v>7</v>
       </c>
       <c r="C77" s="81" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>7</v>
@@ -4842,10 +4842,10 @@
         <v>11</v>
       </c>
       <c r="C78" s="43" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D78" s="41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E78" s="42" t="s">
         <v>11</v>
@@ -4905,14 +4905,14 @@
       <c r="B81" s="53"/>
       <c r="C81" s="89"/>
       <c r="D81" s="96" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E81" s="97"/>
       <c r="F81" s="97"/>
       <c r="G81" s="97"/>
       <c r="H81" s="98"/>
       <c r="I81" s="126" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J81" s="127"/>
       <c r="K81" s="127"/>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="82" spans="1:16" ht="15" customHeight="1">
       <c r="A82" s="132" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B82" s="133"/>
       <c r="C82" s="134"/>
@@ -4937,10 +4937,10 @@
         <v>3</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>3</v>
@@ -4967,10 +4967,10 @@
         <v>11</v>
       </c>
       <c r="H83" s="56" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J83" s="36" t="s">
         <v>11</v>
@@ -4981,7 +4981,7 @@
       <c r="L83" s="25"/>
       <c r="M83" s="26"/>
       <c r="N83" s="135" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O83" s="136"/>
       <c r="P83" s="137"/>
@@ -4994,10 +4994,10 @@
         <v>7</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>10</v>
@@ -5016,10 +5016,10 @@
         <v>28</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N84" s="90" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="O84" s="90" t="s">
         <v>3</v>
@@ -5043,7 +5043,7 @@
       <c r="L85" s="23"/>
       <c r="M85" s="6"/>
       <c r="N85" s="129" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O85" s="130"/>
       <c r="P85" s="131"/>
@@ -5063,13 +5063,13 @@
         <v>2</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O86" s="11" t="s">
         <v>7</v>
@@ -5091,10 +5091,10 @@
         <v>3</v>
       </c>
       <c r="H87" s="81" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J87" s="19" t="s">
         <v>3</v>
@@ -5121,10 +5121,10 @@
         <v>7</v>
       </c>
       <c r="H88" s="81" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J88" s="19" t="s">
         <v>7</v>
@@ -5151,10 +5151,10 @@
         <v>11</v>
       </c>
       <c r="H89" s="43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J89" s="59" t="s">
         <v>11</v>
@@ -5165,7 +5165,7 @@
       <c r="L89" s="25"/>
       <c r="M89" s="26"/>
       <c r="N89" s="132" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O89" s="133"/>
       <c r="P89" s="134"/>
@@ -5181,17 +5181,17 @@
       <c r="H90" s="45"/>
       <c r="I90" s="91"/>
       <c r="J90" s="31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K90" s="31" t="s">
         <v>18</v>
       </c>
       <c r="L90" s="92"/>
       <c r="M90" s="32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N90" s="48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O90" s="49" t="s">
         <v>3</v>
@@ -5215,19 +5215,19 @@
       <c r="L91" s="23"/>
       <c r="M91" s="6"/>
       <c r="N91" s="129" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O91" s="130"/>
       <c r="P91" s="131"/>
     </row>
     <row r="92" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A92" s="123" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B92" s="124"/>
       <c r="C92" s="125"/>
       <c r="D92" s="132" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E92" s="133"/>
       <c r="F92" s="134"/>
@@ -5235,17 +5235,17 @@
       <c r="H92" s="38"/>
       <c r="I92" s="93"/>
       <c r="J92" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K92" s="11" t="s">
         <v>18</v>
       </c>
       <c r="L92" s="94"/>
       <c r="M92" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O92" s="11" t="s">
         <v>28</v>
@@ -5262,10 +5262,10 @@
         <v>28</v>
       </c>
       <c r="C93" s="95" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>3</v>
@@ -5286,22 +5286,22 @@
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A94" s="48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B94" s="49" t="s">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E94" s="49" t="s">
         <v>3</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G94" s="28"/>
       <c r="H94" s="29"/>

--- a/Konekcije.xlsx
+++ b/Konekcije.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleksandra.seva\Desktop\LineFailure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EDD3B1-527B-4673-A219-42FDAA8C57C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A964634-BC8B-4F57-907C-60B98274AD77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,9 +181,6 @@
     <t>port-3: LL 22 (BLK-MST)/BLK3 (PLV)</t>
   </si>
   <si>
-    <t>LL22 (JPAKL MO - ATCU II/Banjaluka)/MST</t>
-  </si>
-  <si>
     <t>unit-18</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>port-3: LL 20 (BLK-TZL)/BLK3 (PLV)</t>
   </si>
   <si>
-    <t>LL 20 (Tuzla - Banjaluka/Mahovljani)/TZL</t>
-  </si>
-  <si>
     <t>UDR</t>
   </si>
   <si>
@@ -461,6 +455,12 @@
   </si>
   <si>
     <t>LL 15 (Tuzla - Nedzarici)/TZL</t>
+  </si>
+  <si>
+    <t>LL 20 (Tuzla - Mahovljani)/TZL</t>
+  </si>
+  <si>
+    <t>LL22 (JPAKL MO - ATCU II)/MST</t>
   </si>
 </sst>
 </file>
@@ -1534,6 +1534,51 @@
     <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1543,96 +1588,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1640,33 +1595,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1677,6 +1605,78 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2829,30 +2829,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="108" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="111" t="s">
-        <v>118</v>
-      </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="96" t="s">
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="132" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="97"/>
-      <c r="P1" s="98"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="113"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2865,7 +2865,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="96" t="s">
+      <c r="N3" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="97"/>
-      <c r="P3" s="98"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="113"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" s="18" t="s">
@@ -2990,11 +2990,11 @@
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="99" t="s">
+      <c r="N5" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="100"/>
-      <c r="P5" s="101"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="125"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
       <c r="A6" s="30" t="s">
@@ -3094,11 +3094,11 @@
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="114" t="s">
+      <c r="N8" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="O8" s="115"/>
-      <c r="P8" s="116"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="140"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1">
       <c r="A9" s="44"/>
@@ -3121,7 +3121,7 @@
         <v>29</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>7</v>
@@ -3168,11 +3168,11 @@
       <c r="K11" s="46"/>
       <c r="L11" s="46"/>
       <c r="M11" s="47"/>
-      <c r="N11" s="120" t="s">
+      <c r="N11" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="O11" s="121"/>
-      <c r="P11" s="122"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="104"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1">
       <c r="A12" s="29"/>
@@ -3218,11 +3218,11 @@
       <c r="K13" s="46"/>
       <c r="L13" s="46"/>
       <c r="M13" s="47"/>
-      <c r="N13" s="96" t="s">
+      <c r="N13" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="97"/>
-      <c r="P13" s="98"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="113"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="29"/>
@@ -3268,11 +3268,11 @@
       <c r="K15" s="46"/>
       <c r="L15" s="46"/>
       <c r="M15" s="47"/>
-      <c r="N15" s="96" t="s">
+      <c r="N15" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="O15" s="97"/>
-      <c r="P15" s="98"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="113"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
       <c r="A16" s="29"/>
@@ -3330,11 +3330,11 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="99" t="s">
+      <c r="N17" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="100"/>
-      <c r="P17" s="101"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="125"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="29"/>
@@ -3380,11 +3380,11 @@
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="120" t="s">
+      <c r="N19" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="O19" s="121"/>
-      <c r="P19" s="122"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="104"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1">
       <c r="A20" s="29"/>
@@ -3453,16 +3453,16 @@
       <c r="P22" s="29"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A23" s="114" t="s">
+      <c r="A23" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="117" t="s">
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="143"/>
       <c r="G23" s="28"/>
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
@@ -3482,7 +3482,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="23"/>
@@ -3506,10 +3506,10 @@
         <v>11</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>3</v>
@@ -3536,7 +3536,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
@@ -3560,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="25"/>
@@ -3584,10 +3584,10 @@
         <v>46</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>46</v>
@@ -3643,18 +3643,18 @@
       <c r="P30" s="29"/>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1">
-      <c r="A31" s="102" t="s">
+      <c r="A31" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="103"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="99" t="s">
+      <c r="B31" s="127"/>
+      <c r="C31" s="128"/>
+      <c r="D31" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="101"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="124"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="125"/>
       <c r="I31" s="51"/>
       <c r="J31" s="53"/>
       <c r="K31" s="53"/>
@@ -3685,11 +3685,11 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="132" t="s">
+      <c r="I32" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="133"/>
-      <c r="K32" s="134"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="101"/>
       <c r="L32" s="28"/>
       <c r="M32" s="29"/>
       <c r="N32" s="29"/>
@@ -3718,13 +3718,13 @@
         <v>52</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L33" s="28"/>
       <c r="M33" s="29"/>
@@ -3740,10 +3740,10 @@
         <v>3</v>
       </c>
       <c r="C34" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="30" t="s">
         <v>55</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>56</v>
       </c>
       <c r="E34" s="31" t="s">
         <v>3</v>
@@ -3753,11 +3753,11 @@
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="135" t="s">
-        <v>57</v>
-      </c>
-      <c r="J34" s="136"/>
-      <c r="K34" s="137"/>
+      <c r="I34" s="105" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="106"/>
+      <c r="K34" s="107"/>
       <c r="L34" s="28"/>
       <c r="M34" s="29"/>
       <c r="N34" s="29"/>
@@ -3777,16 +3777,16 @@
         <v>11</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L35" s="28"/>
       <c r="M35" s="29"/>
@@ -3867,16 +3867,16 @@
       <c r="P39" s="29"/>
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A40" s="132" t="s">
+      <c r="A40" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="133"/>
-      <c r="C40" s="134"/>
-      <c r="D40" s="132" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="133"/>
-      <c r="F40" s="134"/>
+      <c r="B40" s="100"/>
+      <c r="C40" s="101"/>
+      <c r="D40" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="100"/>
+      <c r="F40" s="101"/>
       <c r="G40" s="28"/>
       <c r="H40" s="29"/>
       <c r="I40" s="29"/>
@@ -3896,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="23"/>
@@ -3920,10 +3920,10 @@
         <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -3950,7 +3950,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="14"/>
@@ -3974,7 +3974,7 @@
         <v>30</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="25"/>
@@ -3992,22 +3992,22 @@
     </row>
     <row r="45" spans="1:16" ht="15.95" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E45" s="31" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G45" s="28"/>
       <c r="H45" s="29"/>
@@ -4022,13 +4022,13 @@
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1">
       <c r="A46" s="67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="69" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="70"/>
@@ -4135,25 +4135,25 @@
       <c r="P51" s="29"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1">
-      <c r="A52" s="120" t="s">
+      <c r="A52" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="121"/>
-      <c r="C52" s="122"/>
-      <c r="D52" s="138" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="139"/>
-      <c r="F52" s="139"/>
-      <c r="G52" s="139"/>
-      <c r="H52" s="140"/>
-      <c r="I52" s="96" t="s">
+      <c r="B52" s="103"/>
+      <c r="C52" s="104"/>
+      <c r="D52" s="108" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52" s="109"/>
+      <c r="F52" s="109"/>
+      <c r="G52" s="109"/>
+      <c r="H52" s="110"/>
+      <c r="I52" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="J52" s="97"/>
-      <c r="K52" s="97"/>
-      <c r="L52" s="97"/>
-      <c r="M52" s="98"/>
+      <c r="J52" s="112"/>
+      <c r="K52" s="112"/>
+      <c r="L52" s="112"/>
+      <c r="M52" s="113"/>
       <c r="N52" s="51"/>
       <c r="O52" s="53"/>
       <c r="P52" s="53"/>
@@ -4172,11 +4172,11 @@
       <c r="K53" s="79"/>
       <c r="L53" s="79"/>
       <c r="M53" s="80"/>
-      <c r="N53" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="O53" s="130"/>
-      <c r="P53" s="131"/>
+      <c r="N53" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="O53" s="115"/>
+      <c r="P53" s="116"/>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
@@ -4186,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -4208,10 +4208,10 @@
         <v>11</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O54" s="11" t="s">
         <v>10</v>
@@ -4233,10 +4233,10 @@
         <v>7</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>10</v>
@@ -4258,10 +4258,10 @@
         <v>11</v>
       </c>
       <c r="C56" s="81" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>11</v>
@@ -4280,13 +4280,13 @@
         <v>28</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N56" s="126" t="s">
-        <v>75</v>
-      </c>
-      <c r="O56" s="127"/>
-      <c r="P56" s="128"/>
+        <v>72</v>
+      </c>
+      <c r="N56" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="O56" s="97"/>
+      <c r="P56" s="98"/>
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1">
       <c r="A57" s="18" t="s">
@@ -4296,10 +4296,10 @@
         <v>10</v>
       </c>
       <c r="C57" s="81" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>10</v>
@@ -4318,10 +4318,10 @@
         <v>30</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O57" s="11" t="s">
         <v>10</v>
@@ -4338,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="C58" s="81" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>3</v>
@@ -4368,10 +4368,10 @@
         <v>7</v>
       </c>
       <c r="C59" s="81" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>7</v>
@@ -4398,10 +4398,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>11</v>
@@ -4433,10 +4433,10 @@
         <v>10</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>11</v>
@@ -4464,11 +4464,11 @@
       <c r="K62" s="46"/>
       <c r="L62" s="88"/>
       <c r="M62" s="26"/>
-      <c r="N62" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="O62" s="130"/>
-      <c r="P62" s="131"/>
+      <c r="N62" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="O62" s="115"/>
+      <c r="P62" s="116"/>
     </row>
     <row r="63" spans="1:16" ht="15" customHeight="1">
       <c r="A63" s="29"/>
@@ -4488,10 +4488,10 @@
         <v>10</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O63" s="11" t="s">
         <v>10</v>
@@ -4514,11 +4514,11 @@
       <c r="K64" s="23"/>
       <c r="L64" s="23"/>
       <c r="M64" s="6"/>
-      <c r="N64" s="126" t="s">
-        <v>75</v>
-      </c>
-      <c r="O64" s="127"/>
-      <c r="P64" s="128"/>
+      <c r="N64" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="O64" s="97"/>
+      <c r="P64" s="98"/>
     </row>
     <row r="65" spans="1:16" ht="15" customHeight="1">
       <c r="A65" s="29"/>
@@ -4538,10 +4538,10 @@
         <v>30</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O65" s="11" t="s">
         <v>10</v>
@@ -4568,7 +4568,7 @@
         <v>33</v>
       </c>
       <c r="M66" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N66" s="82"/>
       <c r="O66" s="44"/>
@@ -4665,18 +4665,18 @@
       <c r="P71" s="29"/>
     </row>
     <row r="72" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A72" s="141" t="s">
-        <v>87</v>
-      </c>
-      <c r="B72" s="142"/>
-      <c r="C72" s="143"/>
-      <c r="D72" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="E72" s="130"/>
-      <c r="F72" s="130"/>
-      <c r="G72" s="130"/>
-      <c r="H72" s="131"/>
+      <c r="A72" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" s="118"/>
+      <c r="C72" s="119"/>
+      <c r="D72" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="E72" s="115"/>
+      <c r="F72" s="115"/>
+      <c r="G72" s="115"/>
+      <c r="H72" s="116"/>
       <c r="I72" s="28"/>
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
@@ -4694,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>3</v>
@@ -4724,10 +4724,10 @@
         <v>11</v>
       </c>
       <c r="C74" s="56" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E74" s="36" t="s">
         <v>11</v>
@@ -4763,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I75" s="28"/>
       <c r="J75" s="29"/>
@@ -4782,10 +4782,10 @@
         <v>3</v>
       </c>
       <c r="C76" s="81" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>3</v>
@@ -4812,10 +4812,10 @@
         <v>7</v>
       </c>
       <c r="C77" s="81" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>7</v>
@@ -4842,10 +4842,10 @@
         <v>11</v>
       </c>
       <c r="C78" s="43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D78" s="41" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E78" s="42" t="s">
         <v>11</v>
@@ -4904,30 +4904,30 @@
       <c r="A81" s="53"/>
       <c r="B81" s="53"/>
       <c r="C81" s="89"/>
-      <c r="D81" s="96" t="s">
-        <v>98</v>
-      </c>
-      <c r="E81" s="97"/>
-      <c r="F81" s="97"/>
-      <c r="G81" s="97"/>
-      <c r="H81" s="98"/>
-      <c r="I81" s="126" t="s">
-        <v>75</v>
-      </c>
-      <c r="J81" s="127"/>
-      <c r="K81" s="127"/>
-      <c r="L81" s="127"/>
-      <c r="M81" s="128"/>
+      <c r="D81" s="111" t="s">
+        <v>96</v>
+      </c>
+      <c r="E81" s="112"/>
+      <c r="F81" s="112"/>
+      <c r="G81" s="112"/>
+      <c r="H81" s="113"/>
+      <c r="I81" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="J81" s="97"/>
+      <c r="K81" s="97"/>
+      <c r="L81" s="97"/>
+      <c r="M81" s="98"/>
       <c r="N81" s="28"/>
       <c r="O81" s="29"/>
       <c r="P81" s="29"/>
     </row>
     <row r="82" spans="1:16" ht="15" customHeight="1">
-      <c r="A82" s="132" t="s">
-        <v>99</v>
-      </c>
-      <c r="B82" s="133"/>
-      <c r="C82" s="134"/>
+      <c r="A82" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="B82" s="100"/>
+      <c r="C82" s="101"/>
       <c r="D82" s="13"/>
       <c r="E82" s="16"/>
       <c r="F82" s="3" t="s">
@@ -4937,10 +4937,10 @@
         <v>3</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>3</v>
@@ -4967,10 +4967,10 @@
         <v>11</v>
       </c>
       <c r="H83" s="56" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J83" s="36" t="s">
         <v>11</v>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="L83" s="25"/>
       <c r="M83" s="26"/>
-      <c r="N83" s="135" t="s">
-        <v>57</v>
-      </c>
-      <c r="O83" s="136"/>
-      <c r="P83" s="137"/>
+      <c r="N83" s="105" t="s">
+        <v>56</v>
+      </c>
+      <c r="O83" s="106"/>
+      <c r="P83" s="107"/>
     </row>
     <row r="84" spans="1:16" ht="15" customHeight="1">
       <c r="A84" s="10" t="s">
@@ -4994,10 +4994,10 @@
         <v>7</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>10</v>
@@ -5016,10 +5016,10 @@
         <v>28</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N84" s="90" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O84" s="90" t="s">
         <v>3</v>
@@ -5042,11 +5042,11 @@
       <c r="K85" s="23"/>
       <c r="L85" s="23"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="O85" s="130"/>
-      <c r="P85" s="131"/>
+      <c r="N85" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="O85" s="115"/>
+      <c r="P85" s="116"/>
     </row>
     <row r="86" spans="1:16" ht="15" customHeight="1">
       <c r="A86" s="29"/>
@@ -5066,10 +5066,10 @@
         <v>30</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O86" s="11" t="s">
         <v>7</v>
@@ -5091,10 +5091,10 @@
         <v>3</v>
       </c>
       <c r="H87" s="81" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J87" s="19" t="s">
         <v>3</v>
@@ -5121,10 +5121,10 @@
         <v>7</v>
       </c>
       <c r="H88" s="81" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J88" s="19" t="s">
         <v>7</v>
@@ -5151,10 +5151,10 @@
         <v>11</v>
       </c>
       <c r="H89" s="43" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J89" s="59" t="s">
         <v>11</v>
@@ -5164,11 +5164,11 @@
       </c>
       <c r="L89" s="25"/>
       <c r="M89" s="26"/>
-      <c r="N89" s="132" t="s">
+      <c r="N89" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="O89" s="133"/>
-      <c r="P89" s="134"/>
+      <c r="O89" s="100"/>
+      <c r="P89" s="101"/>
     </row>
     <row r="90" spans="1:16" ht="15" customHeight="1">
       <c r="A90" s="29"/>
@@ -5188,10 +5188,10 @@
       </c>
       <c r="L90" s="92"/>
       <c r="M90" s="32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N90" s="48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O90" s="49" t="s">
         <v>3</v>
@@ -5214,23 +5214,23 @@
       <c r="K91" s="23"/>
       <c r="L91" s="23"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="O91" s="130"/>
-      <c r="P91" s="131"/>
+      <c r="N91" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="O91" s="115"/>
+      <c r="P91" s="116"/>
     </row>
     <row r="92" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="A92" s="123" t="s">
-        <v>114</v>
-      </c>
-      <c r="B92" s="124"/>
-      <c r="C92" s="125"/>
-      <c r="D92" s="132" t="s">
-        <v>99</v>
-      </c>
-      <c r="E92" s="133"/>
-      <c r="F92" s="134"/>
+      <c r="A92" s="120" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92" s="121"/>
+      <c r="C92" s="122"/>
+      <c r="D92" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="E92" s="100"/>
+      <c r="F92" s="101"/>
       <c r="G92" s="28"/>
       <c r="H92" s="38"/>
       <c r="I92" s="93"/>
@@ -5242,10 +5242,10 @@
       </c>
       <c r="L92" s="94"/>
       <c r="M92" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O92" s="11" t="s">
         <v>28</v>
@@ -5262,10 +5262,10 @@
         <v>28</v>
       </c>
       <c r="C93" s="95" t="s">
+        <v>131</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>3</v>
@@ -5286,22 +5286,22 @@
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" thickBot="1">
       <c r="A94" s="48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B94" s="49" t="s">
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D94" s="48" t="s">
         <v>134</v>
-      </c>
-      <c r="D94" s="48" t="s">
-        <v>136</v>
       </c>
       <c r="E94" s="49" t="s">
         <v>3</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G94" s="28"/>
       <c r="H94" s="29"/>
@@ -5316,6 +5316,29 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="D81:H81"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="I81:M81"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="N85:P85"/>
     <mergeCell ref="N56:P56"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="N19:P19"/>
@@ -5331,29 +5354,6 @@
     <mergeCell ref="D72:H72"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="I81:M81"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="A23:C23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>

--- a/Konekcije.xlsx
+++ b/Konekcije.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleksandra.seva\Desktop\LineFailure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A964634-BC8B-4F57-907C-60B98274AD77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0644FBD9-FE78-4CCC-9818-A29F994DF421}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="146">
   <si>
     <t>KOZ</t>
   </si>
@@ -353,9 +353,6 @@
   </si>
   <si>
     <t>port-3: LL_Zastita-RR_B/SJJ4 (BTM)</t>
-  </si>
-  <si>
-    <t>port-6: RR 21 (SJJ-MST)/SJJ4 (BTM)</t>
   </si>
   <si>
     <t>BUK APP</t>
@@ -1534,6 +1531,96 @@
     <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1543,6 +1630,15 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1552,15 +1648,6 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1577,24 +1664,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1605,78 +1674,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2829,30 +2826,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="132" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="108" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="135" t="s">
-        <v>116</v>
-      </c>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="111" t="s">
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="112"/>
-      <c r="P1" s="113"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="98"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2865,7 +2862,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -2922,11 +2919,11 @@
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="111" t="s">
+      <c r="N3" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="112"/>
-      <c r="P3" s="113"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="98"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" s="18" t="s">
@@ -2990,11 +2987,11 @@
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="123" t="s">
+      <c r="N5" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="124"/>
-      <c r="P5" s="125"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="101"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
       <c r="A6" s="30" t="s">
@@ -3094,11 +3091,11 @@
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="138" t="s">
+      <c r="N8" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="O8" s="139"/>
-      <c r="P8" s="140"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="116"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1">
       <c r="A9" s="44"/>
@@ -3121,7 +3118,7 @@
         <v>29</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>7</v>
@@ -3168,11 +3165,11 @@
       <c r="K11" s="46"/>
       <c r="L11" s="46"/>
       <c r="M11" s="47"/>
-      <c r="N11" s="102" t="s">
+      <c r="N11" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="O11" s="103"/>
-      <c r="P11" s="104"/>
+      <c r="O11" s="121"/>
+      <c r="P11" s="122"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1">
       <c r="A12" s="29"/>
@@ -3218,11 +3215,11 @@
       <c r="K13" s="46"/>
       <c r="L13" s="46"/>
       <c r="M13" s="47"/>
-      <c r="N13" s="111" t="s">
+      <c r="N13" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O13" s="112"/>
-      <c r="P13" s="113"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="98"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="29"/>
@@ -3268,11 +3265,11 @@
       <c r="K15" s="46"/>
       <c r="L15" s="46"/>
       <c r="M15" s="47"/>
-      <c r="N15" s="111" t="s">
+      <c r="N15" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="O15" s="112"/>
-      <c r="P15" s="113"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="98"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
       <c r="A16" s="29"/>
@@ -3330,11 +3327,11 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="123" t="s">
+      <c r="N17" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="124"/>
-      <c r="P17" s="125"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="101"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="29"/>
@@ -3380,11 +3377,11 @@
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="102" t="s">
+      <c r="N19" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="O19" s="103"/>
-      <c r="P19" s="104"/>
+      <c r="O19" s="121"/>
+      <c r="P19" s="122"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1">
       <c r="A20" s="29"/>
@@ -3453,16 +3450,16 @@
       <c r="P22" s="29"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A23" s="138" t="s">
+      <c r="A23" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141" t="s">
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="142"/>
-      <c r="F23" s="143"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
       <c r="G23" s="28"/>
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
@@ -3482,7 +3479,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="23"/>
@@ -3506,10 +3503,10 @@
         <v>11</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>3</v>
@@ -3536,7 +3533,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
@@ -3560,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="25"/>
@@ -3584,10 +3581,10 @@
         <v>46</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>46</v>
@@ -3643,18 +3640,18 @@
       <c r="P30" s="29"/>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1">
-      <c r="A31" s="126" t="s">
+      <c r="A31" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="127"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="123" t="s">
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="124"/>
-      <c r="F31" s="124"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="125"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="101"/>
       <c r="I31" s="51"/>
       <c r="J31" s="53"/>
       <c r="K31" s="53"/>
@@ -3685,11 +3682,11 @@
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="99" t="s">
+      <c r="I32" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="100"/>
-      <c r="K32" s="101"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="134"/>
       <c r="L32" s="28"/>
       <c r="M32" s="29"/>
       <c r="N32" s="29"/>
@@ -3718,7 +3715,7 @@
         <v>52</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>3</v>
@@ -3753,11 +3750,11 @@
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="105" t="s">
+      <c r="I34" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="J34" s="106"/>
-      <c r="K34" s="107"/>
+      <c r="J34" s="136"/>
+      <c r="K34" s="137"/>
       <c r="L34" s="28"/>
       <c r="M34" s="29"/>
       <c r="N34" s="29"/>
@@ -3780,7 +3777,7 @@
         <v>57</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>3</v>
@@ -3867,16 +3864,16 @@
       <c r="P39" s="29"/>
     </row>
     <row r="40" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A40" s="99" t="s">
+      <c r="A40" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="100"/>
-      <c r="C40" s="101"/>
-      <c r="D40" s="99" t="s">
+      <c r="B40" s="133"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="100"/>
-      <c r="F40" s="101"/>
+      <c r="E40" s="133"/>
+      <c r="F40" s="134"/>
       <c r="G40" s="28"/>
       <c r="H40" s="29"/>
       <c r="I40" s="29"/>
@@ -3923,7 +3920,7 @@
         <v>60</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -4001,7 +3998,7 @@
         <v>63</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E45" s="31" t="s">
         <v>3</v>
@@ -4135,25 +4132,25 @@
       <c r="P51" s="29"/>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1">
-      <c r="A52" s="102" t="s">
+      <c r="A52" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="103"/>
-      <c r="C52" s="104"/>
-      <c r="D52" s="108" t="s">
+      <c r="B52" s="121"/>
+      <c r="C52" s="122"/>
+      <c r="D52" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="109"/>
-      <c r="G52" s="109"/>
-      <c r="H52" s="110"/>
-      <c r="I52" s="111" t="s">
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
+      <c r="H52" s="140"/>
+      <c r="I52" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="J52" s="112"/>
-      <c r="K52" s="112"/>
-      <c r="L52" s="112"/>
-      <c r="M52" s="113"/>
+      <c r="J52" s="97"/>
+      <c r="K52" s="97"/>
+      <c r="L52" s="97"/>
+      <c r="M52" s="98"/>
       <c r="N52" s="51"/>
       <c r="O52" s="53"/>
       <c r="P52" s="53"/>
@@ -4172,11 +4169,11 @@
       <c r="K53" s="79"/>
       <c r="L53" s="79"/>
       <c r="M53" s="80"/>
-      <c r="N53" s="114" t="s">
+      <c r="N53" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="O53" s="115"/>
-      <c r="P53" s="116"/>
+      <c r="O53" s="130"/>
+      <c r="P53" s="131"/>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
@@ -4208,10 +4205,10 @@
         <v>11</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O54" s="11" t="s">
         <v>10</v>
@@ -4236,7 +4233,7 @@
         <v>69</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>10</v>
@@ -4282,11 +4279,11 @@
       <c r="M56" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="N56" s="96" t="s">
+      <c r="N56" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="O56" s="97"/>
-      <c r="P56" s="98"/>
+      <c r="O56" s="127"/>
+      <c r="P56" s="128"/>
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1">
       <c r="A57" s="18" t="s">
@@ -4318,10 +4315,10 @@
         <v>30</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O57" s="11" t="s">
         <v>10</v>
@@ -4464,11 +4461,11 @@
       <c r="K62" s="46"/>
       <c r="L62" s="88"/>
       <c r="M62" s="26"/>
-      <c r="N62" s="114" t="s">
+      <c r="N62" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="O62" s="115"/>
-      <c r="P62" s="116"/>
+      <c r="O62" s="130"/>
+      <c r="P62" s="131"/>
     </row>
     <row r="63" spans="1:16" ht="15" customHeight="1">
       <c r="A63" s="29"/>
@@ -4488,10 +4485,10 @@
         <v>10</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O63" s="11" t="s">
         <v>10</v>
@@ -4514,11 +4511,11 @@
       <c r="K64" s="23"/>
       <c r="L64" s="23"/>
       <c r="M64" s="6"/>
-      <c r="N64" s="96" t="s">
+      <c r="N64" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="O64" s="97"/>
-      <c r="P64" s="98"/>
+      <c r="O64" s="127"/>
+      <c r="P64" s="128"/>
     </row>
     <row r="65" spans="1:16" ht="15" customHeight="1">
       <c r="A65" s="29"/>
@@ -4538,10 +4535,10 @@
         <v>30</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O65" s="11" t="s">
         <v>10</v>
@@ -4665,18 +4662,18 @@
       <c r="P71" s="29"/>
     </row>
     <row r="72" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A72" s="117" t="s">
+      <c r="A72" s="141" t="s">
         <v>85</v>
       </c>
-      <c r="B72" s="118"/>
-      <c r="C72" s="119"/>
-      <c r="D72" s="114" t="s">
+      <c r="B72" s="142"/>
+      <c r="C72" s="143"/>
+      <c r="D72" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="E72" s="115"/>
-      <c r="F72" s="115"/>
-      <c r="G72" s="115"/>
-      <c r="H72" s="116"/>
+      <c r="E72" s="130"/>
+      <c r="F72" s="130"/>
+      <c r="G72" s="130"/>
+      <c r="H72" s="131"/>
       <c r="I72" s="28"/>
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
@@ -4697,7 +4694,7 @@
         <v>86</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>3</v>
@@ -4904,30 +4901,30 @@
       <c r="A81" s="53"/>
       <c r="B81" s="53"/>
       <c r="C81" s="89"/>
-      <c r="D81" s="111" t="s">
+      <c r="D81" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="E81" s="112"/>
-      <c r="F81" s="112"/>
-      <c r="G81" s="112"/>
-      <c r="H81" s="113"/>
-      <c r="I81" s="96" t="s">
+      <c r="E81" s="97"/>
+      <c r="F81" s="97"/>
+      <c r="G81" s="97"/>
+      <c r="H81" s="98"/>
+      <c r="I81" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="J81" s="97"/>
-      <c r="K81" s="97"/>
-      <c r="L81" s="97"/>
-      <c r="M81" s="98"/>
+      <c r="J81" s="127"/>
+      <c r="K81" s="127"/>
+      <c r="L81" s="127"/>
+      <c r="M81" s="128"/>
       <c r="N81" s="28"/>
       <c r="O81" s="29"/>
       <c r="P81" s="29"/>
     </row>
     <row r="82" spans="1:16" ht="15" customHeight="1">
-      <c r="A82" s="99" t="s">
+      <c r="A82" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="B82" s="100"/>
-      <c r="C82" s="101"/>
+      <c r="B82" s="133"/>
+      <c r="C82" s="134"/>
       <c r="D82" s="13"/>
       <c r="E82" s="16"/>
       <c r="F82" s="3" t="s">
@@ -4980,11 +4977,11 @@
       </c>
       <c r="L83" s="25"/>
       <c r="M83" s="26"/>
-      <c r="N83" s="105" t="s">
+      <c r="N83" s="135" t="s">
         <v>56</v>
       </c>
-      <c r="O83" s="106"/>
-      <c r="P83" s="107"/>
+      <c r="O83" s="136"/>
+      <c r="P83" s="137"/>
     </row>
     <row r="84" spans="1:16" ht="15" customHeight="1">
       <c r="A84" s="10" t="s">
@@ -4994,10 +4991,10 @@
         <v>7</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>10</v>
@@ -5019,7 +5016,7 @@
         <v>102</v>
       </c>
       <c r="N84" s="90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O84" s="90" t="s">
         <v>3</v>
@@ -5042,11 +5039,11 @@
       <c r="K85" s="23"/>
       <c r="L85" s="23"/>
       <c r="M85" s="6"/>
-      <c r="N85" s="114" t="s">
+      <c r="N85" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="O85" s="115"/>
-      <c r="P85" s="116"/>
+      <c r="O85" s="130"/>
+      <c r="P85" s="131"/>
     </row>
     <row r="86" spans="1:16" ht="15" customHeight="1">
       <c r="A86" s="29"/>
@@ -5164,11 +5161,11 @@
       </c>
       <c r="L89" s="25"/>
       <c r="M89" s="26"/>
-      <c r="N89" s="99" t="s">
+      <c r="N89" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="O89" s="100"/>
-      <c r="P89" s="101"/>
+      <c r="O89" s="133"/>
+      <c r="P89" s="134"/>
     </row>
     <row r="90" spans="1:16" ht="15" customHeight="1">
       <c r="A90" s="29"/>
@@ -5180,25 +5177,13 @@
       <c r="G90" s="44"/>
       <c r="H90" s="45"/>
       <c r="I90" s="91"/>
-      <c r="J90" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="K90" s="31" t="s">
-        <v>18</v>
-      </c>
+      <c r="J90" s="31"/>
+      <c r="K90" s="31"/>
       <c r="L90" s="92"/>
-      <c r="M90" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="N90" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="O90" s="49" t="s">
-        <v>3</v>
-      </c>
-      <c r="P90" s="50" t="s">
-        <v>18</v>
-      </c>
+      <c r="M90" s="32"/>
+      <c r="N90" s="48"/>
+      <c r="O90" s="49"/>
+      <c r="P90" s="50"/>
     </row>
     <row r="91" spans="1:16" ht="15" customHeight="1">
       <c r="A91" s="53"/>
@@ -5214,23 +5199,23 @@
       <c r="K91" s="23"/>
       <c r="L91" s="23"/>
       <c r="M91" s="6"/>
-      <c r="N91" s="114" t="s">
+      <c r="N91" s="129" t="s">
         <v>66</v>
       </c>
-      <c r="O91" s="115"/>
-      <c r="P91" s="116"/>
+      <c r="O91" s="130"/>
+      <c r="P91" s="131"/>
     </row>
     <row r="92" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="A92" s="120" t="s">
-        <v>112</v>
-      </c>
-      <c r="B92" s="121"/>
-      <c r="C92" s="122"/>
-      <c r="D92" s="99" t="s">
+      <c r="A92" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="124"/>
+      <c r="C92" s="125"/>
+      <c r="D92" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="E92" s="100"/>
-      <c r="F92" s="101"/>
+      <c r="E92" s="133"/>
+      <c r="F92" s="134"/>
       <c r="G92" s="28"/>
       <c r="H92" s="38"/>
       <c r="I92" s="93"/>
@@ -5242,10 +5227,10 @@
       </c>
       <c r="L92" s="94"/>
       <c r="M92" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="N92" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="N92" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="O92" s="11" t="s">
         <v>28</v>
@@ -5262,10 +5247,10 @@
         <v>28</v>
       </c>
       <c r="C93" s="95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>3</v>
@@ -5292,10 +5277,10 @@
         <v>3</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E94" s="49" t="s">
         <v>3</v>
@@ -5316,6 +5301,29 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="N83:P83"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="I52:M52"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="N53:P53"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="N62:P62"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="D81:H81"/>
+    <mergeCell ref="N64:P64"/>
+    <mergeCell ref="I81:M81"/>
+    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N89:P89"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="N85:P85"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="N17:P17"/>
@@ -5331,29 +5339,6 @@
     <mergeCell ref="N13:P13"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="N64:P64"/>
-    <mergeCell ref="I81:M81"/>
-    <mergeCell ref="N91:P91"/>
-    <mergeCell ref="N89:P89"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="N85:P85"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="N83:P83"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="I52:M52"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="N53:P53"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="N62:P62"/>
-    <mergeCell ref="D72:H72"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
